--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PrajyotDabhade\Documents\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7857C3D2-8786-4D28-AEBA-B2903158947C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8B134D-1CFF-444F-BF3E-26D80975BFA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
   </bookViews>
@@ -25,24 +25,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>BULK IDs</t>
   </si>
   <si>
+    <t>20250902-0004</t>
+  </si>
+  <si>
     <t>20250902-0002</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>SECURE RESOURCES_WITHDRAWN</t>
   </si>
   <si>
     <t>SECURE RESOURCES_ACCEPTED</t>
   </si>
   <si>
-    <t>Current Status</t>
-  </si>
-  <si>
-    <t>20250903-0009</t>
+    <t>20250902-0008</t>
+  </si>
+  <si>
+    <t>SECURE RESOURCES_NOT STARTED</t>
   </si>
 </sst>
 </file>
@@ -409,12 +415,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.08984375" customWidth="1"/>
     <col min="2" max="2" width="33.26953125" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -422,23 +427,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PrajyotDabhade\Documents\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8B134D-1CFF-444F-BF3E-26D80975BFA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249FE258-C1A7-4A1A-AD81-876F888D47A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
   </bookViews>
@@ -25,30 +25,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>BULK IDs</t>
   </si>
   <si>
-    <t>20250902-0004</t>
+    <t>Captured Current Status</t>
   </si>
   <si>
-    <t>20250902-0002</t>
+    <t>Status After Execution</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>SECURE RESOURCES_WITHDRAWN</t>
-  </si>
-  <si>
-    <t>SECURE RESOURCES_ACCEPTED</t>
-  </si>
-  <si>
-    <t>20250902-0008</t>
-  </si>
-  <si>
-    <t>SECURE RESOURCES_NOT STARTED</t>
+    <t>20250904-0002</t>
   </si>
 </sst>
 </file>
@@ -415,43 +403,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" customWidth="1"/>
-    <col min="2" max="2" width="33.26953125" customWidth="1"/>
+    <col min="1" max="1" width="16.08984375" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="33.26953125" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="26.453125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249FE258-C1A7-4A1A-AD81-876F888D47A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB44BE7-78EC-4439-9641-99356A38DD1D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -37,6 +37,12 @@
   </si>
   <si>
     <t>20250904-0002</t>
+  </si>
+  <si>
+    <t>20250905-0010</t>
+  </si>
+  <si>
+    <t>20250905-0012</t>
   </si>
 </sst>
 </file>
@@ -86,9 +92,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -403,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.08984375" customWidth="1" collapsed="1"/>
@@ -424,8 +433,21 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB44BE7-78EC-4439-9641-99356A38DD1D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{60FE3913-C551-48B5-8839-739E0FCE3B89}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
+    <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -39,16 +39,26 @@
     <t>20250904-0002</t>
   </si>
   <si>
-    <t>20250905-0010</t>
-  </si>
-  <si>
-    <t>20250905-0012</t>
+    <t>20250905-0018</t>
+  </si>
+  <si>
+    <t>20250905-0019</t>
+  </si>
+  <si>
+    <t>SECURE RESOURCES_ACCEPTED</t>
+  </si>
+  <si>
+    <t>Processed</t>
+  </si>
+  <si>
+    <t>Unassign Pass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -90,20 +100,20 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -120,10 +130,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -158,7 +168,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -210,7 +220,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -321,21 +331,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -352,7 +362,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -404,20 +414,20 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:C7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="33.26953125" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="26.453125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" width="16.08984375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="33.26953125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="26.453125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -435,6 +445,12 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -450,7 +466,7 @@
       <c r="B7" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{60FE3913-C551-48B5-8839-739E0FCE3B89}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr documentId="13_ncr:1_{6A2CE91C-6490-438C-A2A6-A333CFAD6250}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
   <bookViews>
     <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -39,12 +39,12 @@
     <t>20250904-0002</t>
   </si>
   <si>
-    <t>20250905-0018</t>
-  </si>
-  <si>
     <t>20250905-0019</t>
   </si>
   <si>
+    <t>20250905-0020</t>
+  </si>
+  <si>
     <t>SECURE RESOURCES_ACCEPTED</t>
   </si>
   <si>
@@ -52,6 +52,12 @@
   </si>
   <si>
     <t>Unassign Pass</t>
+  </si>
+  <si>
+    <t>SECURE RESOURCES_WITHDRAWN</t>
+  </si>
+  <si>
+    <t>Not Found</t>
   </si>
 </sst>
 </file>
@@ -443,7 +449,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -454,12 +460,21 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">

--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{6A2CE91C-6490-438C-A2A6-A333CFAD6250}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727502AE-4C86-4FB0-B1FC-82608A66D9B0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -36,35 +36,25 @@
     <t>Status After Execution</t>
   </si>
   <si>
-    <t>20250904-0002</t>
-  </si>
-  <si>
-    <t>20250905-0019</t>
-  </si>
-  <si>
-    <t>20250905-0020</t>
-  </si>
-  <si>
-    <t>SECURE RESOURCES_ACCEPTED</t>
-  </si>
-  <si>
-    <t>Processed</t>
-  </si>
-  <si>
-    <t>Unassign Pass</t>
-  </si>
-  <si>
-    <t>SECURE RESOURCES_WITHDRAWN</t>
-  </si>
-  <si>
-    <t>Not Found</t>
+    <t>Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unassign Driver </t>
+  </si>
+  <si>
+    <t>Withdrawn Tender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unassign Order </t>
+  </si>
+  <si>
+    <t>20250908-0001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -106,20 +96,25 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -136,10 +131,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -174,7 +169,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -226,7 +221,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -337,21 +332,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -368,7 +363,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -420,68 +415,62 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:D7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="16.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="33.26953125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="26.453125" collapsed="true"/>
+    <col min="1" max="1" width="16.08984375" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.90625" customWidth="1"/>
+    <col min="3" max="3" width="33.26953125" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
+    <col min="5" max="5" width="18.90625" customWidth="1"/>
+    <col min="6" max="6" width="21.36328125" customWidth="1"/>
+    <col min="7" max="7" width="26.453125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B7" s="2"/>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727502AE-4C86-4FB0-B1FC-82608A66D9B0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{8382D0AA-7B29-42FA-85A2-E63B037DAD29}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
+    <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -49,13 +49,35 @@
   </si>
   <si>
     <t>20250908-0001</t>
+  </si>
+  <si>
+    <t>SO_17560390</t>
+  </si>
+  <si>
+    <t>Not Found</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Unassign Pass</t>
+  </si>
+  <si>
+    <t>SECURE RESOURCES_WITHDRAWN</t>
+  </si>
+  <si>
+    <t>Unassign Fail</t>
+  </si>
+  <si>
+    <t>20250909-0017</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +89,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -95,26 +125,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="2">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="5">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle builtinId="8" name="Hyperlink" xfId="1"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -131,10 +162,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -169,7 +200,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -221,7 +252,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -332,21 +363,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -363,7 +394,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -415,24 +446,24 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="18.90625" customWidth="1"/>
-    <col min="3" max="3" width="33.26953125" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="16.26953125" customWidth="1"/>
-    <col min="5" max="5" width="18.90625" customWidth="1"/>
-    <col min="6" max="6" width="21.36328125" customWidth="1"/>
-    <col min="7" max="7" width="26.453125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" width="16.08984375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="18.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="33.26953125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" width="16.26953125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="18.90625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" width="21.36328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" width="26.453125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -461,6 +492,41 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -470,7 +536,10 @@
       <c r="F7" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink display="https://otmgtm-dev1-summit1.otmgtm.us-ashburn-1.ocs.oraclecloud.com/GC3/glog.webserver.finder.WindowOpenFramesetServlet/nss?url=OrderReleaseCustManagement%3Fmanager_layout_gid%3DORDER_RELEASE_VIEW%26query_name%3Dglog.server.query.order.OrderReleaseQuery%26management_action%3Dview%26finder_set_gid%3DBXC.ORDER%20RELEASE_UPDATE%26pk%3DBXC.SO_17560390" r:id="rId1" ref="B3" xr:uid="{DFE22562-5641-4994-A3A9-DA912354E6D0}"/>
+  </hyperlinks>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{8382D0AA-7B29-42FA-85A2-E63B037DAD29}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr documentId="13_ncr:1_{295CBB16-DBBE-41EF-8F08-F96FA8EE8BBA}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
   <bookViews>
     <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -48,28 +48,16 @@
     <t xml:space="preserve">Unassign Order </t>
   </si>
   <si>
-    <t>20250908-0001</t>
+    <t>20250909-0018</t>
+  </si>
+  <si>
+    <t>SECURE RESOURCES_ACCEPTED</t>
+  </si>
+  <si>
+    <t>Unassign Pass</t>
   </si>
   <si>
     <t>SO_17560390</t>
-  </si>
-  <si>
-    <t>Not Found</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Unassign Pass</t>
-  </si>
-  <si>
-    <t>SECURE RESOURCES_WITHDRAWN</t>
-  </si>
-  <si>
-    <t>Unassign Fail</t>
-  </si>
-  <si>
-    <t>20250909-0017</t>
   </si>
 </sst>
 </file>
@@ -129,7 +117,7 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
     <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
@@ -137,7 +125,6 @@
     <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -454,11 +441,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="16.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="18.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="23.81640625" collapsed="true"/>
     <col min="3" max="3" customWidth="true" width="33.26953125" collapsed="true"/>
     <col min="4" max="4" customWidth="true" width="16.26953125" collapsed="true"/>
     <col min="5" max="5" customWidth="true" width="18.90625" collapsed="true"/>
@@ -490,56 +477,36 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink display="https://otmgtm-dev1-summit1.otmgtm.us-ashburn-1.ocs.oraclecloud.com/GC3/glog.webserver.finder.WindowOpenFramesetServlet/nss?url=OrderReleaseCustManagement%3Fmanager_layout_gid%3DORDER_RELEASE_VIEW%26query_name%3Dglog.server.query.order.OrderReleaseQuery%26management_action%3Dview%26finder_set_gid%3DBXC.ORDER%20RELEASE_UPDATE%26pk%3DBXC.SO_17560390" r:id="rId1" ref="B3" xr:uid="{DFE22562-5641-4994-A3A9-DA912354E6D0}"/>
-  </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{295CBB16-DBBE-41EF-8F08-F96FA8EE8BBA}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr documentId="13_ncr:1_{90431B8F-928C-4619-9244-BCEB0AB6BE31}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
   <bookViews>
     <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="20">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -36,9 +36,6 @@
     <t>Status After Execution</t>
   </si>
   <si>
-    <t>Order</t>
-  </si>
-  <si>
     <t xml:space="preserve">Unassign Driver </t>
   </si>
   <si>
@@ -51,13 +48,43 @@
     <t>20250909-0018</t>
   </si>
   <si>
+    <t xml:space="preserve">Order </t>
+  </si>
+  <si>
+    <t>20250909-0021</t>
+  </si>
+  <si>
+    <t>20250909-0027</t>
+  </si>
+  <si>
+    <t>20250909-0029</t>
+  </si>
+  <si>
+    <t>Not Found</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>SECURE RESOURCES_WITHDRAWN</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>SO_17560390</t>
+  </si>
+  <si>
+    <t>Unassign Pass</t>
+  </si>
+  <si>
     <t>SECURE RESOURCES_ACCEPTED</t>
   </si>
   <si>
-    <t>Unassign Pass</t>
-  </si>
-  <si>
-    <t>SO_17560390</t>
+    <t>SO_17464632</t>
+  </si>
+  <si>
+    <t>SO_17428794, SO_17413866</t>
   </si>
 </sst>
 </file>
@@ -65,7 +92,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,14 +104,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -104,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -112,23 +131,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="2" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle builtinId="8" name="Hyperlink" xfId="1"/>
+  <cellStyles count="1">
     <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -458,19 +489,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>2</v>
@@ -478,25 +509,88 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">

--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{90431B8F-928C-4619-9244-BCEB0AB6BE31}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr documentId="13_ncr:1_{8AA7AEF2-3730-4B1A-9978-BB9E5D1C57F6}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
   <bookViews>
-    <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
+    <workbookView activeTab="1" windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
+    <sheet name="Bulk IDs Reset" r:id="rId1" sheetId="1"/>
+    <sheet name="Bulk IDs Created" r:id="rId2" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -45,46 +46,43 @@
     <t xml:space="preserve">Unassign Order </t>
   </si>
   <si>
-    <t>20250909-0018</t>
-  </si>
-  <si>
     <t xml:space="preserve">Order </t>
   </si>
   <si>
-    <t>20250909-0021</t>
-  </si>
-  <si>
-    <t>20250909-0027</t>
-  </si>
-  <si>
-    <t>20250909-0029</t>
-  </si>
-  <si>
-    <t>Not Found</t>
+    <t>Sales order</t>
+  </si>
+  <si>
+    <t>Bulk Ids</t>
+  </si>
+  <si>
+    <t>20250910-0013</t>
+  </si>
+  <si>
+    <t>SECURE RESOURCES_WITHDRAWN</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>SECURE RESOURCES_WITHDRAWN</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>SO_17560390</t>
   </si>
   <si>
+    <t>SO_17205914</t>
+  </si>
+  <si>
+    <t>SO_17560390, SO_17205914</t>
+  </si>
+  <si>
     <t>Unassign Pass</t>
   </si>
   <si>
-    <t>SECURE RESOURCES_ACCEPTED</t>
-  </si>
-  <si>
-    <t>SO_17464632</t>
-  </si>
-  <si>
-    <t>SO_17428794, SO_17413866</t>
+    <t>Unassign Successful</t>
+  </si>
+  <si>
+    <t>20250910-0014</t>
+  </si>
+  <si>
+    <t>20250910-0015</t>
   </si>
 </sst>
 </file>
@@ -476,7 +474,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="16.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="23.81640625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="65.1796875" collapsed="true"/>
     <col min="3" max="3" customWidth="true" width="33.26953125" collapsed="true"/>
     <col min="4" max="4" customWidth="true" width="16.26953125" collapsed="true"/>
     <col min="5" max="5" customWidth="true" width="18.90625" collapsed="true"/>
@@ -489,7 +487,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -509,87 +507,24 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -603,4 +538,42 @@
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B496C953-DA2D-4863-9575-E7BEA4F6DBB3}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="28.0" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="21.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{8AA7AEF2-3730-4B1A-9978-BB9E5D1C57F6}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr documentId="13_ncr:1_{75EE651E-0E1F-4D98-8350-0B4D7D87A2FD}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
+    <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
   </bookViews>
   <sheets>
     <sheet name="Bulk IDs Reset" r:id="rId1" sheetId="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -55,34 +55,19 @@
     <t>Bulk Ids</t>
   </si>
   <si>
-    <t>20250910-0013</t>
+    <t>20250910-0017</t>
+  </si>
+  <si>
+    <t>SECURE RESOURCES_ACCEPTED</t>
+  </si>
+  <si>
+    <t>Unassign Pass</t>
   </si>
   <si>
     <t>SECURE RESOURCES_WITHDRAWN</t>
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>SO_17560390</t>
-  </si>
-  <si>
-    <t>SO_17205914</t>
-  </si>
-  <si>
-    <t>SO_17560390, SO_17205914</t>
-  </si>
-  <si>
-    <t>Unassign Pass</t>
-  </si>
-  <si>
-    <t>Unassign Successful</t>
-  </si>
-  <si>
-    <t>20250910-0014</t>
-  </si>
-  <si>
-    <t>20250910-0015</t>
   </si>
 </sst>
 </file>
@@ -474,7 +459,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="16.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="65.1796875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="26.7265625" collapsed="true"/>
     <col min="3" max="3" customWidth="true" width="33.26953125" collapsed="true"/>
     <col min="4" max="4" customWidth="true" width="16.26953125" collapsed="true"/>
     <col min="5" max="5" customWidth="true" width="18.90625" collapsed="true"/>
@@ -509,23 +494,14 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -542,7 +518,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B496C953-DA2D-4863-9575-E7BEA4F6DBB3}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="28.0" collapsed="true"/>
@@ -557,22 +533,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{75EE651E-0E1F-4D98-8350-0B4D7D87A2FD}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr documentId="13_ncr:1_{6A240A18-CFD7-431E-9716-D64B290827D7}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
   <bookViews>
     <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="25">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -55,19 +55,52 @@
     <t>Bulk Ids</t>
   </si>
   <si>
-    <t>20250910-0017</t>
+    <t xml:space="preserve">Failed Retry  </t>
+  </si>
+  <si>
+    <t>Early pickup date</t>
+  </si>
+  <si>
+    <t>Late delivery Date</t>
+  </si>
+  <si>
+    <t>SO_17560390</t>
+  </si>
+  <si>
+    <t>20250911-0001</t>
+  </si>
+  <si>
+    <t>20250903-0015</t>
+  </si>
+  <si>
+    <t>20250903-0031</t>
+  </si>
+  <si>
+    <t>20250903-0012</t>
+  </si>
+  <si>
+    <t>20250903-0013</t>
+  </si>
+  <si>
+    <t>20250903-0014</t>
+  </si>
+  <si>
+    <t>Not Found</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>20250811-0011</t>
+  </si>
+  <si>
+    <t>20250811-0012</t>
+  </si>
+  <si>
+    <t>20250811-0013</t>
   </si>
   <si>
     <t>SECURE RESOURCES_ACCEPTED</t>
-  </si>
-  <si>
-    <t>Unassign Pass</t>
-  </si>
-  <si>
-    <t>SECURE RESOURCES_WITHDRAWN</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -75,7 +108,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,8 +124,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,8 +150,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -129,17 +186,62 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE8E8E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE8E8E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE8E8E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE8E8E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE8E8E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE8E8E8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE8E8E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8E8E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE8E8E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyBorder="1" applyFont="1" borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0"/>
+    <xf applyBorder="1" applyFill="1" applyFont="1" borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,8 +557,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="16.08984375" collapsed="true"/>
     <col min="2" max="2" customWidth="true" width="26.7265625" collapsed="true"/>
@@ -465,9 +567,10 @@
     <col min="5" max="5" customWidth="true" width="18.90625" collapsed="true"/>
     <col min="6" max="6" customWidth="true" width="21.36328125" collapsed="true"/>
     <col min="7" max="7" customWidth="true" width="26.453125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" width="22.08984375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row customFormat="1" ht="15" r="1" s="3" spans="1:8" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -489,26 +592,116 @@
       <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="H1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
+    </row>
+    <row ht="15" r="2" spans="1:8" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row ht="15" r="3" spans="1:8" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row ht="15" r="4" spans="1:8" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row ht="15" r="5" spans="1:8" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row ht="15" r="6" spans="1:8" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -518,19 +711,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B496C953-DA2D-4863-9575-E7BEA4F6DBB3}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="28.0" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="21.7265625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="22.54296875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="21.54296875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" width="25.54296875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{6A240A18-CFD7-431E-9716-D64B290827D7}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C91FF97-ABEC-46BA-9744-10F847260CE9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bulk IDs Reset" r:id="rId1" sheetId="1"/>
-    <sheet name="Bulk IDs Created" r:id="rId2" sheetId="2"/>
+    <sheet name="Bulk IDs Reset" sheetId="1" r:id="rId1"/>
+    <sheet name="Bulk IDs Created" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="177">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -49,12 +49,6 @@
     <t xml:space="preserve">Order </t>
   </si>
   <si>
-    <t>Sales order</t>
-  </si>
-  <si>
-    <t>Bulk Ids</t>
-  </si>
-  <si>
     <t xml:space="preserve">Failed Retry  </t>
   </si>
   <si>
@@ -64,12 +58,6 @@
     <t>Late delivery Date</t>
   </si>
   <si>
-    <t>SO_17560390</t>
-  </si>
-  <si>
-    <t>20250911-0001</t>
-  </si>
-  <si>
     <t>20250903-0015</t>
   </si>
   <si>
@@ -101,14 +89,481 @@
   </si>
   <si>
     <t>SECURE RESOURCES_ACCEPTED</t>
+  </si>
+  <si>
+    <t>20250801-0001</t>
+  </si>
+  <si>
+    <t>20250801-0002</t>
+  </si>
+  <si>
+    <t>20250801-0003</t>
+  </si>
+  <si>
+    <t>20250801-0004</t>
+  </si>
+  <si>
+    <t>20250801-0005</t>
+  </si>
+  <si>
+    <t>20250801-0006</t>
+  </si>
+  <si>
+    <t>20250801-0007</t>
+  </si>
+  <si>
+    <t>20250801-0008</t>
+  </si>
+  <si>
+    <t>20250801-0009</t>
+  </si>
+  <si>
+    <t>20250801-0010</t>
+  </si>
+  <si>
+    <t>20250801-0011</t>
+  </si>
+  <si>
+    <t>20250801-0012</t>
+  </si>
+  <si>
+    <t>20250801-0013</t>
+  </si>
+  <si>
+    <t>20250801-0014</t>
+  </si>
+  <si>
+    <t>20250801-0015</t>
+  </si>
+  <si>
+    <t>20250806-0001</t>
+  </si>
+  <si>
+    <t>20250806-0002</t>
+  </si>
+  <si>
+    <t>20250806-0003</t>
+  </si>
+  <si>
+    <t>20250806-0004</t>
+  </si>
+  <si>
+    <t>20250806-0005</t>
+  </si>
+  <si>
+    <t>20250806-0006</t>
+  </si>
+  <si>
+    <t>20250806-0007</t>
+  </si>
+  <si>
+    <t>20250806-0008</t>
+  </si>
+  <si>
+    <t>20250806-0009</t>
+  </si>
+  <si>
+    <t>20250811-0001</t>
+  </si>
+  <si>
+    <t>20250811-0002</t>
+  </si>
+  <si>
+    <t>20250811-0003</t>
+  </si>
+  <si>
+    <t>20250811-0004</t>
+  </si>
+  <si>
+    <t>20250811-0005</t>
+  </si>
+  <si>
+    <t>20250811-0006</t>
+  </si>
+  <si>
+    <t>20250811-0007</t>
+  </si>
+  <si>
+    <t>20250811-0008</t>
+  </si>
+  <si>
+    <t>20250811-0009</t>
+  </si>
+  <si>
+    <t>20250811-0010</t>
+  </si>
+  <si>
+    <t>20250811-0014</t>
+  </si>
+  <si>
+    <t>20250811-0015</t>
+  </si>
+  <si>
+    <t>20250811-0016</t>
+  </si>
+  <si>
+    <t>20250811-0017</t>
+  </si>
+  <si>
+    <t>20250811-0018</t>
+  </si>
+  <si>
+    <t>20250811-0019</t>
+  </si>
+  <si>
+    <t>20250822-0007</t>
+  </si>
+  <si>
+    <t>20250822-0008</t>
+  </si>
+  <si>
+    <t>20250811-0020</t>
+  </si>
+  <si>
+    <t>20250811-0021</t>
+  </si>
+  <si>
+    <t>20250811-0023</t>
+  </si>
+  <si>
+    <t>20250811-0024</t>
+  </si>
+  <si>
+    <t>20250811-0025</t>
+  </si>
+  <si>
+    <t>20250811-0026</t>
+  </si>
+  <si>
+    <t>20250811-0027</t>
+  </si>
+  <si>
+    <t>20250811-0028</t>
+  </si>
+  <si>
+    <t>20250811-0029</t>
+  </si>
+  <si>
+    <t>20250811-0030</t>
+  </si>
+  <si>
+    <t>20250811-0022</t>
+  </si>
+  <si>
+    <t>20250903-0007</t>
+  </si>
+  <si>
+    <t>20250903-0008</t>
+  </si>
+  <si>
+    <t>20250903-0010</t>
+  </si>
+  <si>
+    <t>20250903-0017</t>
+  </si>
+  <si>
+    <t>20250903-0021</t>
+  </si>
+  <si>
+    <t>20250903-0026</t>
+  </si>
+  <si>
+    <t>20250903-0028</t>
+  </si>
+  <si>
+    <t>20250903-0030</t>
+  </si>
+  <si>
+    <t>Unassign Pass</t>
+  </si>
+  <si>
+    <t>SECURE RESOURCES_WITHDRAWN</t>
+  </si>
+  <si>
+    <t>SO_17205914</t>
+  </si>
+  <si>
+    <t>Unassign Successful</t>
+  </si>
+  <si>
+    <t>20250911-0005</t>
+  </si>
+  <si>
+    <t>TENDER_UNTENDER</t>
+  </si>
+  <si>
+    <t>SECURE RESOURCES_NOT STARTED</t>
+  </si>
+  <si>
+    <t>SO_17556375_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17571914_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17424391_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17579137_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17580158_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17578656_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17556784_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17578644_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17423117_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17569007_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17571292_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17576512_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17578764_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17556730_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17576700_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17572960_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>Unassign Failed</t>
+  </si>
+  <si>
+    <t>2025-09-13 00:00 America/New_York</t>
+  </si>
+  <si>
+    <t>2025-10-12 23:59 America/New_York</t>
+  </si>
+  <si>
+    <t>20250911-0006</t>
+  </si>
+  <si>
+    <t>20250911-0007</t>
+  </si>
+  <si>
+    <t>20250911-0008</t>
+  </si>
+  <si>
+    <t>20250911-0009</t>
+  </si>
+  <si>
+    <t>20250911-0010</t>
+  </si>
+  <si>
+    <t>20250911-0011</t>
+  </si>
+  <si>
+    <t>20250911-0012</t>
+  </si>
+  <si>
+    <t>20250911-0013</t>
+  </si>
+  <si>
+    <t>20250911-0014</t>
+  </si>
+  <si>
+    <t>20250911-0015</t>
+  </si>
+  <si>
+    <t>20250911-0016</t>
+  </si>
+  <si>
+    <t>20250911-0017</t>
+  </si>
+  <si>
+    <t>20250911-0018</t>
+  </si>
+  <si>
+    <t>20250911-0019</t>
+  </si>
+  <si>
+    <t>20250911-0020</t>
+  </si>
+  <si>
+    <t>20250911-0021</t>
+  </si>
+  <si>
+    <t>SO_17569666_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17577017_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17453507_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17579813_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17579560_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17580759_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17568569_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17580255_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17568002_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17581161_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17557783_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17574493_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17557712_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17566595_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17565721_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17440292_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17572926_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17566399_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17547576_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17576644_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17573076_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17568923_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17579296_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17579306_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>SO_17566361_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>20250912-0001</t>
+  </si>
+  <si>
+    <t>20250912-0002</t>
+  </si>
+  <si>
+    <t>20250912-0003</t>
+  </si>
+  <si>
+    <t>20250912-0004</t>
+  </si>
+  <si>
+    <t>20250912-0005</t>
+  </si>
+  <si>
+    <t>20250912-0006</t>
+  </si>
+  <si>
+    <t>20250912-0007</t>
+  </si>
+  <si>
+    <t>20250912-0008</t>
+  </si>
+  <si>
+    <t>20250912-0009</t>
+  </si>
+  <si>
+    <t>20250912-0010</t>
+  </si>
+  <si>
+    <t>20250912-0011</t>
+  </si>
+  <si>
+    <t>20250912-0012</t>
+  </si>
+  <si>
+    <t>20250912-0013</t>
+  </si>
+  <si>
+    <t>20250912-0014</t>
+  </si>
+  <si>
+    <t>20250912-0015</t>
+  </si>
+  <si>
+    <t>20250912-0016</t>
+  </si>
+  <si>
+    <t>20250912-0017</t>
+  </si>
+  <si>
+    <t>20250912-0018</t>
+  </si>
+  <si>
+    <t>20250912-0019</t>
+  </si>
+  <si>
+    <t>20250912-0020</t>
+  </si>
+  <si>
+    <t>20250912-0021</t>
+  </si>
+  <si>
+    <t>20250912-0022</t>
+  </si>
+  <si>
+    <t>20250912-0023</t>
+  </si>
+  <si>
+    <t>20250912-0024</t>
+  </si>
+  <si>
+    <t>20250912-0025</t>
+  </si>
+  <si>
+    <t>Sales Order IDs</t>
+  </si>
+  <si>
+    <t>Bulk IDs</t>
+  </si>
+  <si>
+    <t>SO_17556375_20250915_07-07-2025_BEL_V2H, SO_17571914_20250915_07-07-2025_BEL_V2H, SO_17424391_20250915_07-07-2025_BEL_V2H, SO_17579137_20250915_07-07-2025_BEL_V2H, SO_17580158_20250915_07-07-2025_BEL_V2H, SO_17578656_20250915_07-07-2025_BEL_V2H, SO_17556784_20250915_07-07-2025_BEL_V2H, SO_17578644_20250915_07-07-2025_BEL_V2H, SO_17423117_20250915_07-07-2025_BEL_V2H, SO_17569007_20250915_07-07-2025_BEL_V2H, SO_17571292_20250915_07-07-2025_BEL_V2H, SO_17576512_20250915_07-07-2025_BEL_V2H, SO_17578764_20250915_07-07-2025_BEL_V2H, SO_17556730_20250915_07-07-2025_BEL_V2H, SO_17576700_20250915_07-07-2025_BEL_V2H, SO_17572960_20250915_07-07-2025_BEL_V2H, SO_17569666_20250915_07-07-2025_BEL_V2H, SO_17577017_20250915_07-07-2025_BEL_V2H, SO_17453507_20250915_07-07-2025_BEL_V2H, SO_17579813_20250915_07-07-2025_BEL_V2H, SO_17579560_20250915_07-07-2025_BEL_V2H, SO_17580759_20250915_07-07-2025_BEL_V2H, SO_17568569_20250915_07-07-2025_BEL_V2H, SO_17580255_20250915_07-07-2025_BEL_V2H, SO_17568002_20250915_07-07-2025_BEL_V2H, SO_17581161_20250915_07-07-2025_BEL_V2H, SO_17557783_20250915_07-07-2025_BEL_V2H, SO_17574493_20250915_07-07-2025_BEL_V2H, SO_17557712_20250915_07-07-2025_BEL_V2H, SO_17566595_20250915_07-07-2025_BEL_V2H, SO_17565721_20250915_07-07-2025_BEL_V2H, SO_17440292_20250915_07-07-2025_BEL_V2H, SO_17572926_20250915_07-07-2025_BEL_V2H, SO_17566399_20250915_07-07-2025_BEL_V2H, SO_17547576_20250915_07-07-2025_BEL_V2H, SO_17576644_20250915_07-07-2025_BEL_V2H, SO_17573076_20250915_07-07-2025_BEL_V2H, SO_17568923_20250915_07-07-2025_BEL_V2H, SO_17579296_20250915_07-07-2025_BEL_V2H, SO_17579306_20250915_07-07-2025_BEL_V2H, SO_17566361_20250915_07-07-2025_BEL_V2H</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,14 +585,19 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,14 +616,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -201,54 +655,32 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFE8E8E8"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFE8E8E8"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFE8E8E8"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE8E8E8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE8E8E8"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyBorder="1" applyFont="1" borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0"/>
-    <xf applyBorder="1" applyFill="1" applyFont="1" borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -265,10 +697,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -303,7 +735,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -355,7 +787,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -466,21 +898,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -497,7 +929,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -549,200 +981,3219 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
-  <dimension ref="A1:I9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F13729-7653-44B7-8A16-E2DDDD80648E}">
+  <dimension ref="A1:S88"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="16.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="26.7265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="33.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" width="16.26953125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="18.90625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" width="21.36328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" width="26.453125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" width="22.08984375" collapsed="true"/>
+    <col min="1" max="1" width="16.08984375" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="21.54296875" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="38.36328125" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.90625" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="21.36328125" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="26.453125" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="22.08984375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" ht="15" r="1" s="3" spans="1:8" thickBot="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="15" thickBot="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row ht="15" r="2" spans="1:8" thickBot="1">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15" thickBot="1">
       <c r="A2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" ht="15" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+    </row>
+    <row r="5" spans="1:19" ht="15" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" spans="1:19" ht="15" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+    </row>
+    <row r="7" spans="1:19" ht="15" thickBot="1">
+      <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" spans="1:19" ht="15" thickBot="1">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" ht="15" thickBot="1">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" ht="15" thickBot="1">
+      <c r="A10" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row ht="15" r="3" spans="1:8" thickBot="1">
-      <c r="A3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" ht="15" thickBot="1">
+      <c r="A11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" ht="15" thickBot="1">
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" ht="15" thickBot="1">
+      <c r="A13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" ht="15" thickBot="1">
+      <c r="A14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" ht="15" thickBot="1">
+      <c r="A15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" ht="15" thickBot="1">
+      <c r="A16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="1:19" ht="15" thickBot="1">
+      <c r="A17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="1:19" ht="15" thickBot="1">
+      <c r="A18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="1:19" ht="15" thickBot="1">
+      <c r="A19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="1:19" ht="15" thickBot="1">
+      <c r="A20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="1:19" ht="15" thickBot="1">
+      <c r="A21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="1:19" ht="15" thickBot="1">
+      <c r="A22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="1:19" ht="15" thickBot="1">
+      <c r="A23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="1:19" ht="15" thickBot="1">
+      <c r="A24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="1:19" ht="15" thickBot="1">
+      <c r="A25" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="1:19" ht="15" thickBot="1">
+      <c r="A26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="1:19" ht="15" thickBot="1">
+      <c r="A27" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="1:19" ht="15" thickBot="1">
+      <c r="A28" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="1:19" ht="15" thickBot="1">
+      <c r="A29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="1:19" ht="15" thickBot="1">
+      <c r="A30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="1:19" ht="15" thickBot="1">
+      <c r="A31" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="1:19" ht="15" thickBot="1">
+      <c r="A32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="1:19" ht="15" thickBot="1">
+      <c r="A33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="1:19" ht="15" thickBot="1">
+      <c r="A34" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="1:19" ht="15" thickBot="1">
+      <c r="A35" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="36" spans="1:19" ht="15" thickBot="1">
+      <c r="A36" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+    </row>
+    <row r="37" spans="1:19" ht="15" thickBot="1">
+      <c r="A37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+    </row>
+    <row r="38" spans="1:19" ht="15" thickBot="1">
+      <c r="A38" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+    </row>
+    <row r="39" spans="1:19" ht="15" thickBot="1">
+      <c r="A39" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="1:19" ht="15" thickBot="1">
+      <c r="A40" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="1:19" ht="15" thickBot="1">
+      <c r="A41" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="1:19" ht="15" thickBot="1">
+      <c r="A42" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="1:19" ht="15" thickBot="1">
+      <c r="A43" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="1:19" ht="15" thickBot="1">
+      <c r="A44" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="1:19" ht="15" thickBot="1">
+      <c r="A45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="1:19" ht="15" thickBot="1">
+      <c r="A46" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row ht="15" r="4" spans="1:8" thickBot="1">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row ht="15" r="5" spans="1:8" thickBot="1">
-      <c r="A5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row ht="15" r="6" spans="1:8" thickBot="1">
-      <c r="A6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="1:19" ht="15" thickBot="1">
+      <c r="A47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="1:19" ht="15" thickBot="1">
+      <c r="A48" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="1:19" ht="15" thickBot="1">
+      <c r="A49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="1:19" ht="15" thickBot="1">
+      <c r="A50" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="1:19" ht="15" thickBot="1">
+      <c r="A51" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="1:19" ht="15" thickBot="1">
+      <c r="A52" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="1:19" ht="15" thickBot="1">
+      <c r="A53" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="1:19" ht="15" thickBot="1">
+      <c r="A54" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="1:19" ht="15" thickBot="1">
+      <c r="A55" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="1:19" ht="15" thickBot="1">
+      <c r="A56" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="1:19" ht="15" thickBot="1">
+      <c r="A57" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="1:19" ht="15" thickBot="1">
+      <c r="A58" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="1:19" ht="15" thickBot="1">
+      <c r="A59" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="1:19" ht="15" thickBot="1">
+      <c r="A60" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="1:19" ht="15" thickBot="1">
+      <c r="A61" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="1:19" ht="15" thickBot="1">
+      <c r="A62" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="1:19" ht="15" thickBot="1">
+      <c r="A63" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="1:19" ht="15" thickBot="1">
+      <c r="A64" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="1:19" ht="15" thickBot="1">
+      <c r="A65" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="1:19" ht="15" thickBot="1">
+      <c r="A66" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="1:19" ht="15" thickBot="1">
+      <c r="A67" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="1:19" ht="15" thickBot="1">
+      <c r="A68" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="1:19" ht="15" thickBot="1">
+      <c r="A69" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="1:19" ht="15" thickBot="1">
+      <c r="A70" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="1:19" ht="15" thickBot="1">
+      <c r="A71" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="3"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="1:19" ht="15" thickBot="1">
+      <c r="A72" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="1:19" ht="15" thickBot="1">
+      <c r="A73" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="1:19" ht="15" thickBot="1">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="1:19" ht="15" thickBot="1">
+      <c r="A75" s="4"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+    </row>
+    <row r="76" spans="1:19">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+    </row>
+    <row r="77" spans="1:19">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+    </row>
+    <row r="79" spans="1:19">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+    </row>
+    <row r="80" spans="1:19">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="6"/>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B496C953-DA2D-4863-9575-E7BEA4F6DBB3}">
-  <dimension ref="A1:E2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B496C953-DA2D-4863-9575-E7BEA4F6DBB3}">
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="28.0" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" width="22.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="21.54296875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" width="25.54296875" collapsed="true"/>
+    <col min="1" max="1" width="39.453125" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="37" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="32.90625" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="25.54296875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" s="6"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" s="6"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="6"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E27" s="6"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="6"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="6"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E30" s="6"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="6"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E32" s="6"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E33" s="6"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" s="6"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E35" s="6"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" s="6"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E37" s="6"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="6"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E39" s="6"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="6"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" s="6"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C91FF97-ABEC-46BA-9744-10F847260CE9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FC6319-4065-481C-B1C2-E574EDBD45CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
   </bookViews>
   <sheets>
     <sheet name="Bulk IDs Reset" sheetId="1" r:id="rId1"/>
@@ -659,7 +659,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -674,6 +674,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1350,7 +1353,7 @@
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="7" t="s">
         <v>176</v>
       </c>
       <c r="C12" s="4" t="s">

--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FC6319-4065-481C-B1C2-E574EDBD45CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0892C9-3FD4-4EED-B6BA-A7242AA9E4F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" activeTab="1" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}"/>
   </bookViews>
   <sheets>
     <sheet name="Bulk IDs Reset" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="178">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -557,6 +557,9 @@
   </si>
   <si>
     <t>SO_17556375_20250915_07-07-2025_BEL_V2H, SO_17571914_20250915_07-07-2025_BEL_V2H, SO_17424391_20250915_07-07-2025_BEL_V2H, SO_17579137_20250915_07-07-2025_BEL_V2H, SO_17580158_20250915_07-07-2025_BEL_V2H, SO_17578656_20250915_07-07-2025_BEL_V2H, SO_17556784_20250915_07-07-2025_BEL_V2H, SO_17578644_20250915_07-07-2025_BEL_V2H, SO_17423117_20250915_07-07-2025_BEL_V2H, SO_17569007_20250915_07-07-2025_BEL_V2H, SO_17571292_20250915_07-07-2025_BEL_V2H, SO_17576512_20250915_07-07-2025_BEL_V2H, SO_17578764_20250915_07-07-2025_BEL_V2H, SO_17556730_20250915_07-07-2025_BEL_V2H, SO_17576700_20250915_07-07-2025_BEL_V2H, SO_17572960_20250915_07-07-2025_BEL_V2H, SO_17569666_20250915_07-07-2025_BEL_V2H, SO_17577017_20250915_07-07-2025_BEL_V2H, SO_17453507_20250915_07-07-2025_BEL_V2H, SO_17579813_20250915_07-07-2025_BEL_V2H, SO_17579560_20250915_07-07-2025_BEL_V2H, SO_17580759_20250915_07-07-2025_BEL_V2H, SO_17568569_20250915_07-07-2025_BEL_V2H, SO_17580255_20250915_07-07-2025_BEL_V2H, SO_17568002_20250915_07-07-2025_BEL_V2H, SO_17581161_20250915_07-07-2025_BEL_V2H, SO_17557783_20250915_07-07-2025_BEL_V2H, SO_17574493_20250915_07-07-2025_BEL_V2H, SO_17557712_20250915_07-07-2025_BEL_V2H, SO_17566595_20250915_07-07-2025_BEL_V2H, SO_17565721_20250915_07-07-2025_BEL_V2H, SO_17440292_20250915_07-07-2025_BEL_V2H, SO_17572926_20250915_07-07-2025_BEL_V2H, SO_17566399_20250915_07-07-2025_BEL_V2H, SO_17547576_20250915_07-07-2025_BEL_V2H, SO_17576644_20250915_07-07-2025_BEL_V2H, SO_17573076_20250915_07-07-2025_BEL_V2H, SO_17568923_20250915_07-07-2025_BEL_V2H, SO_17579296_20250915_07-07-2025_BEL_V2H, SO_17579306_20250915_07-07-2025_BEL_V2H, SO_17566361_20250915_07-07-2025_BEL_V2H</t>
+  </si>
+  <si>
+    <t>Branch Code</t>
   </si>
 </sst>
 </file>
@@ -3481,6 +3484,7 @@
     <col min="2" max="2" width="37" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="32.90625" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="25.54296875" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3495,6 +3499,9 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>175</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:5">

--- a/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
+++ b/Data Files/OTM Test Data/Demo Bulk IDs.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BlueLinx_Automation_Master\Data Files\OTM Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{8382D0AA-7B29-42FA-85A2-E63B037DAD29}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
+  <xr:revisionPtr documentId="13_ncr:1_{BF3C6A51-C498-4BC4-8BFC-81DE17299CE5}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36"/>
   <bookViews>
-    <workbookView windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
+    <workbookView activeTab="1" windowHeight="6810" windowWidth="19200" xWindow="0" xr2:uid="{3033C71C-91B3-45AA-8870-5371DAB13ABE}" yWindow="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
+    <sheet name="Sheet2" r:id="rId2" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>BULK IDs</t>
   </si>
@@ -66,10 +67,25 @@
     <t>SECURE RESOURCES_WITHDRAWN</t>
   </si>
   <si>
-    <t>Unassign Fail</t>
-  </si>
-  <si>
     <t>20250909-0017</t>
+  </si>
+  <si>
+    <t>SO_17401015, SO_17385515, SO_17396172, SO_17401520, SO_17401049</t>
+  </si>
+  <si>
+    <t>SO_17401015</t>
+  </si>
+  <si>
+    <t>SO_17385515</t>
+  </si>
+  <si>
+    <t>SO_17396172</t>
+  </si>
+  <si>
+    <t>SO_17401520</t>
+  </si>
+  <si>
+    <t>SO_17401049</t>
   </si>
 </sst>
 </file>
@@ -493,6 +509,9 @@
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
@@ -508,7 +527,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -542,4 +561,72 @@
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A042424D-1093-44FD-AF35-8259A63891FE}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="22.54296875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="21.36328125" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>